--- a/veterinarian_forms/001_veterinary_release_form--veterinarian_forms.xlsx
+++ b/veterinarian_forms/001_veterinary_release_form--veterinarian_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -661,12 +661,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -728,12 +728,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'hypothyroidism',_'label':_'hypothyroidism'}</t>
+          <t>hypothyroidism</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'hypothyroidism', 'label': 'hypothyroidism'}</t>
+          <t>hypothyroidism</t>
         </is>
       </c>
     </row>
@@ -745,12 +745,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'cancer',_'label':_'cancer'}</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'cancer', 'label': 'cancer'}</t>
+          <t>cancer</t>
         </is>
       </c>
     </row>
@@ -762,12 +762,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'diabetes',_'label':_'diabetes'}</t>
+          <t>diabetes</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'diabetes', 'label': 'diabetes'}</t>
+          <t>diabetes</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'hypertension',_'label':_'hypertension'}</t>
+          <t>hypertension</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'hypertension', 'label': 'hypertension'}</t>
+          <t>hypertension</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'neurodegenerative_disorder',_'label':_'neurodegenerative_disorder'}</t>
+          <t>neurodegenerative_disorder</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'neurodegenerative disorder', 'label': 'neurodegenerative disorder'}</t>
+          <t>neurodegenerative disorder</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'neurodegenerative_disorders',_'label':_'neurodegenerative_disorders'}</t>
+          <t>neurodegenerative_disorders</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'neurodegenerative disorders', 'label': 'neurodegenerative disorders'}</t>
+          <t>neurodegenerative disorders</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'neurodegenerative_disorders',_'label':_'neurodegenerative_disorders'}</t>
+          <t>medical_conditions_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'neurodegenerative disorders', 'label': 'neurodegenerative disorders'}</t>
+          <t>medical conditions 1</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'medical_conditions_1',_'label':_'medical_conditions_1'}</t>
+          <t>medical_conditions_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'medical_conditions_1', 'label': 'medical_conditions_1'}</t>
+          <t>medical conditions 2</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'medical_conditions_2',_'label':_'medical_conditions_2'}</t>
+          <t>medical_conditions_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'medical_conditions_2', 'label': 'medical_conditions_2'}</t>
+          <t>medical conditions 3</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_'medical_conditions_3',_'label':_'medical_conditions_3'}</t>
+          <t>medical_conditions_4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': 'medical_conditions_3', 'label': 'medical_conditions_3'}</t>
+          <t>medical conditions 4</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_17,_'name':_'medical_conditions_4',_'label':_'medical_conditions_4'}</t>
+          <t>medical_conditions_5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 17, 'name': 'medical_conditions_4', 'label': 'medical_conditions_4'}</t>
+          <t>medical conditions 5</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_18,_'name':_'medical_conditions_5',_'label':_'medical_conditions_5'}</t>
+          <t>medical_conditions_6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 18, 'name': 'medical_conditions_5', 'label': 'medical_conditions_5'}</t>
+          <t>medical conditions 6</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_19,_'name':_'medical_conditions_6',_'label':_'medical_conditions_6'}</t>
+          <t>medical_conditions_7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 19, 'name': 'medical_conditions_6', 'label': 'medical_conditions_6'}</t>
+          <t>medical conditions 7</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_'medical_conditions_7',_'label':_'medical_conditions_7'}</t>
+          <t>medical_conditions_8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': 'medical_conditions_7', 'label': 'medical_conditions_7'}</t>
+          <t>medical conditions 8</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'medical_conditions_8',_'label':_'medical_conditions_8'}</t>
+          <t>medical_conditions_9</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'medical_conditions_8', 'label': 'medical_conditions_8'}</t>
+          <t>medical conditions 9</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_'medical_conditions_9',_'label':_'medical_conditions_9'}</t>
+          <t>medical_conditions_10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': 'medical_conditions_9', 'label': 'medical_conditions_9'}</t>
+          <t>medical conditions 10</t>
         </is>
       </c>
     </row>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_23,_'name':_'medical_conditions_10',_'label':_'medical_conditions_10'}</t>
+          <t>medical_conditions_11</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 23, 'name': 'medical_conditions_10', 'label': 'medical_conditions_10'}</t>
+          <t>medical conditions 11</t>
         </is>
       </c>
     </row>
@@ -1017,29 +1017,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_24,_'name':_'medical_conditions_11',_'label':_'medical_conditions_11'}</t>
+          <t>medical_conditions_12</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 24, 'name': 'medical_conditions_11', 'label': 'medical_conditions_11'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>medical_conditions_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'id':_25,_'name':_'medical_conditions_12',_'label':_'medical_conditions_12'}</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'id': 25, 'name': 'medical_conditions_12', 'label': 'medical_conditions_12'}</t>
+          <t>medical conditions 12</t>
         </is>
       </c>
     </row>
